--- a/data/trans_orig/P16A10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106143</t>
+          <t>106651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>145784</t>
+          <t>147643</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121239</t>
+          <t>120727</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>166423</t>
+          <t>167906</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240225</t>
+          <t>240609</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303353</t>
+          <t>302019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>885939</t>
+          <t>884080</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>925580</t>
+          <t>925072</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1148690</t>
+          <t>1147207</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1193874</t>
+          <t>1194386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2043482</t>
+          <t>2044816</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2106610</t>
+          <t>2106226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54206</t>
+          <t>52579</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39039</t>
+          <t>39150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50917</t>
+          <t>51774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83443</t>
+          <t>83744</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1638188</t>
+          <t>1639815</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1663165</t>
+          <t>1664328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1548634</t>
+          <t>1548523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1569380</t>
+          <t>1570000</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3196624</t>
+          <t>3196323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3229150</t>
+          <t>3228293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11474</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30758</t>
+          <t>30269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530732</t>
+          <t>531298</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545899</t>
+          <t>545394</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460866</t>
+          <t>460476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472884</t>
+          <t>472678</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997062</t>
+          <t>997551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1016346</t>
+          <t>1016263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>151478</t>
+          <t>153538</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>205422</t>
+          <t>202598</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154492</t>
+          <t>154493</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204222</t>
+          <t>207824</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319374</t>
+          <t>322063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>391562</t>
+          <t>393925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3070103</t>
+          <t>3072927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3124047</t>
+          <t>3121987</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3174975</t>
+          <t>3171373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3224705</t>
+          <t>3224704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6263160</t>
+          <t>6260797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6335348</t>
+          <t>6332659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2012 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104583</t>
+          <t>105532</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147557</t>
+          <t>147470</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>121764</t>
+          <t>122600</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>166325</t>
+          <t>168402</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237987</t>
+          <t>240791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302388</t>
+          <t>302872</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>825095</t>
+          <t>825182</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>868069</t>
+          <t>867120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1166207</t>
+          <t>1164130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1210768</t>
+          <t>1209932</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2002796</t>
+          <t>2002312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2067197</t>
+          <t>2064393</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>33097</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62512</t>
+          <t>60305</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53461</t>
+          <t>53820</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89878</t>
+          <t>88510</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1897510</t>
+          <t>1899717</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1925891</t>
+          <t>1926925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1720486</t>
+          <t>1719744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1740867</t>
+          <t>1739881</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3625049</t>
+          <t>3626417</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3661466</t>
+          <t>3661107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>17259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5346</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21211</t>
+          <t>21397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463796</t>
+          <t>463073</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476558</t>
+          <t>476322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>449775</t>
+          <t>450233</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>916775</t>
+          <t>916589</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932640</t>
+          <t>932041</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156288</t>
+          <t>155833</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>208910</t>
+          <t>211960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>145424</t>
+          <t>146360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197266</t>
+          <t>195298</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,47 +3415,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>349840</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>313504</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>386567</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>5,56%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>349840</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>316041</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>392097</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3204096</t>
+          <t>3201046</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3256718</t>
+          <t>3257173</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3347825</t>
+          <t>3349793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3399667</t>
+          <t>3398731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,47 +3528,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>95,87%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6157</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6608257</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6571530</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6644593</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>94,97%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>94,44%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>95,9%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6157</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6608257</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6566000</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6642056</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>94,36%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82434</t>
+          <t>80455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113547</t>
+          <t>115657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103953</t>
+          <t>104163</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>149903</t>
+          <t>148881</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>189651</t>
+          <t>194785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250067</t>
+          <t>252541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>640800</t>
+          <t>638690</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671913</t>
+          <t>673892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>844757</t>
+          <t>845779</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>890707</t>
+          <t>890497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1498940</t>
+          <t>1496466</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1559356</t>
+          <t>1554222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,86%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70899</t>
+          <t>72787</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109438</t>
+          <t>108290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>35326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65558</t>
+          <t>65387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>115474</t>
+          <t>116520</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163287</t>
+          <t>161571</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1966947</t>
+          <t>1968095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2005486</t>
+          <t>2003598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1922742</t>
+          <t>1922913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1952805</t>
+          <t>1952974</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3901398</t>
+          <t>3903114</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3949211</t>
+          <t>3948165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27933</t>
+          <t>29278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8360</t>
+          <t>8523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>25240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21926</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46369</t>
+          <t>45925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>518953</t>
+          <t>517608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536892</t>
+          <t>536843</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>524846</t>
+          <t>523900</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540780</t>
+          <t>540617</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1049658</t>
+          <t>1050102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074101</t>
+          <t>1074831</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>177683</t>
+          <t>176755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>234719</t>
+          <t>230791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160922</t>
+          <t>161238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218296</t>
+          <t>219881</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>350968</t>
+          <t>351132</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>432557</t>
+          <t>433055</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3142899</t>
+          <t>3146827</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3199935</t>
+          <t>3200863</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3313804</t>
+          <t>3312219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3371178</t>
+          <t>3370862</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6477161</t>
+          <t>6476663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6558750</t>
+          <t>6558586</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido medicamentos para el corazón en las dos últimas semanas en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65460</t>
+          <t>64752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93050</t>
+          <t>91070</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105030</t>
+          <t>104420</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>132087</t>
+          <t>133261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>176759</t>
+          <t>178091</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217728</t>
+          <t>217600</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,2%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>420892</t>
+          <t>422872</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>448482</t>
+          <t>449190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>619363</t>
+          <t>618189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>646420</t>
+          <t>647030</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047664</t>
+          <t>1047792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1088633</t>
+          <t>1087301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57328</t>
+          <t>56437</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104286</t>
+          <t>104717</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62865</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104027</t>
+          <t>99418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>157276</t>
+          <t>154767</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2186041</t>
+          <t>2185610</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2232999</t>
+          <t>2233890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2174280</t>
+          <t>2174714</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2203240</t>
+          <t>2202978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4370196</t>
+          <t>4372705</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4423445</t>
+          <t>4428054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17985</t>
+          <t>17887</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34399</t>
+          <t>34419</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8082</t>
+          <t>8003</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28966</t>
+          <t>28817</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48875</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612224</t>
+          <t>612204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628638</t>
+          <t>628736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>640151</t>
+          <t>641164</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652381</t>
+          <t>652460</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1258211</t>
+          <t>1257374</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1278120</t>
+          <t>1278269</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>144269</t>
+          <t>138207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214283</t>
+          <t>213386</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>149276</t>
+          <t>146409</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>204620</t>
+          <t>205395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>319534</t>
+          <t>313296</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>408345</t>
+          <t>405725</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3236609</t>
+          <t>3237506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3306623</t>
+          <t>3312685</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3444438</t>
+          <t>3443663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3499782</t>
+          <t>3502649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6691606</t>
+          <t>6694226</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6780417</t>
+          <t>6786655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A10-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P16A10-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106651</t>
+          <t>105697</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147643</t>
+          <t>148259</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120727</t>
+          <t>122819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>167906</t>
+          <t>166956</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240609</t>
+          <t>242931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302019</t>
+          <t>304495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>884080</t>
+          <t>883464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>925072</t>
+          <t>926026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1147207</t>
+          <t>1148157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1194386</t>
+          <t>1192294</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2044816</t>
+          <t>2042340</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2106226</t>
+          <t>2103904</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52579</t>
+          <t>54024</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17484</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>38489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51774</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83744</t>
+          <t>84497</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1639815</t>
+          <t>1638370</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1664328</t>
+          <t>1662675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1548523</t>
+          <t>1549184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1570000</t>
+          <t>1570189</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3196323</t>
+          <t>3195570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3228293</t>
+          <t>3227762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>21207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>15571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>10954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30269</t>
+          <t>29990</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531298</t>
+          <t>530201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545394</t>
+          <t>545935</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460476</t>
+          <t>460841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>472678</t>
+          <t>472917</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>997551</t>
+          <t>997830</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1016263</t>
+          <t>1016866</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153538</t>
+          <t>153862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>202598</t>
+          <t>202443</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>154493</t>
+          <t>155486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>207824</t>
+          <t>205837</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322063</t>
+          <t>319303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>393925</t>
+          <t>393067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3072927</t>
+          <t>3073082</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3121987</t>
+          <t>3121663</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3171373</t>
+          <t>3173360</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3224704</t>
+          <t>3223711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6260797</t>
+          <t>6261655</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6332659</t>
+          <t>6335419</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>105532</t>
+          <t>103740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147470</t>
+          <t>147975</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>122600</t>
+          <t>121936</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168402</t>
+          <t>167858</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>240791</t>
+          <t>240588</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>302872</t>
+          <t>306413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>825182</t>
+          <t>824677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>867120</t>
+          <t>868912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1164130</t>
+          <t>1164674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1209932</t>
+          <t>1210596</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2002312</t>
+          <t>1998771</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2064393</t>
+          <t>2064596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,86%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33097</t>
+          <t>33859</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60305</t>
+          <t>61966</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14760</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35161</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53820</t>
+          <t>54562</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>88510</t>
+          <t>87229</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1899717</t>
+          <t>1898056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1926925</t>
+          <t>1926163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1719744</t>
+          <t>1719029</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1739881</t>
+          <t>1740145</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3626417</t>
+          <t>3627698</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3661107</t>
+          <t>3660365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>16966</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>8084</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>5316</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21397</t>
+          <t>20423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>463073</t>
+          <t>463366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>476322</t>
+          <t>476279</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>450233</t>
+          <t>449570</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>916589</t>
+          <t>917563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>932041</t>
+          <t>932670</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155833</t>
+          <t>153535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211960</t>
+          <t>209263</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146360</t>
+          <t>145608</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195298</t>
+          <t>195942</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>313504</t>
+          <t>314320</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>386567</t>
+          <t>387895</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3201046</t>
+          <t>3203743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3257173</t>
+          <t>3259471</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3349793</t>
+          <t>3349149</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3398731</t>
+          <t>3399483</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6571530</t>
+          <t>6570202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6644593</t>
+          <t>6643777</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80455</t>
+          <t>81469</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115657</t>
+          <t>114217</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104163</t>
+          <t>104259</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148881</t>
+          <t>148484</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>194785</t>
+          <t>197069</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>252541</t>
+          <t>252663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>638690</t>
+          <t>640130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673892</t>
+          <t>672878</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>845779</t>
+          <t>846176</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>890497</t>
+          <t>890401</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1496466</t>
+          <t>1496344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1554222</t>
+          <t>1551938</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72787</t>
+          <t>70452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>108290</t>
+          <t>108808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35326</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65387</t>
+          <t>65330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116520</t>
+          <t>115662</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161571</t>
+          <t>162950</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1968095</t>
+          <t>1967577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2003598</t>
+          <t>2005933</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1922913</t>
+          <t>1922970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1952974</t>
+          <t>1952154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3903114</t>
+          <t>3901735</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3948165</t>
+          <t>3949023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>28544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8523</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25240</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>22148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45925</t>
+          <t>46521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>517608</t>
+          <t>518342</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536843</t>
+          <t>537028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>523900</t>
+          <t>524575</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>540617</t>
+          <t>540699</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1050102</t>
+          <t>1049506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1074831</t>
+          <t>1073879</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>176755</t>
+          <t>174682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230791</t>
+          <t>230081</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>161238</t>
+          <t>163199</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>219881</t>
+          <t>220421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>351132</t>
+          <t>352656</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>433055</t>
+          <t>433783</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3146827</t>
+          <t>3147537</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3200863</t>
+          <t>3202936</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3312219</t>
+          <t>3311679</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3370862</t>
+          <t>3368901</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6476663</t>
+          <t>6475935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6558586</t>
+          <t>6557062</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>78207</t>
+          <t>84350</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64752</t>
+          <t>70154</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91070</t>
+          <t>99533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>118640</t>
+          <t>130241</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>104420</t>
+          <t>113749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>133261</t>
+          <t>146084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>196847</t>
+          <t>214591</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>178091</t>
+          <t>192430</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>217600</t>
+          <t>236495</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>435735</t>
+          <t>493192</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>422872</t>
+          <t>478009</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>449190</t>
+          <t>507388</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>632810</t>
+          <t>689163</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>618189</t>
+          <t>673320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647030</t>
+          <t>705655</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1068545</t>
+          <t>1182355</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1047792</t>
+          <t>1160451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1087301</t>
+          <t>1204516</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>513942</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751450</t>
+          <t>819404</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751450</t>
+          <t>819404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751450</t>
+          <t>819404</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1265392</t>
+          <t>1396946</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265392</t>
+          <t>1396946</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1265392</t>
+          <t>1396946</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83388</t>
+          <t>89980</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56437</t>
+          <t>75297</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104717</t>
+          <t>109122</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>48148</t>
+          <t>54265</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34167</t>
+          <t>43894</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62431</t>
+          <t>68917</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>131536</t>
+          <t>144246</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99418</t>
+          <t>123302</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154767</t>
+          <t>168328</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2206939</t>
+          <t>2140586</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2185610</t>
+          <t>2121444</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2233890</t>
+          <t>2155269</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2188997</t>
+          <t>2116442</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2174714</t>
+          <t>2101790</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2202978</t>
+          <t>2126813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4395936</t>
+          <t>4257028</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4372705</t>
+          <t>4232946</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4428054</t>
+          <t>4277972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237145</t>
+          <t>2170707</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4527472</t>
+          <t>4401274</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>24959</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17887</t>
+          <t>21552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12741</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8003</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19299</t>
+          <t>21526</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>44242</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28817</t>
+          <t>34076</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49712</t>
+          <t>56216</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>621664</t>
+          <t>681685</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>612204</t>
+          <t>671340</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>628736</t>
+          <t>690035</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>647722</t>
+          <t>720537</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>641164</t>
+          <t>713351</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652460</t>
+          <t>725093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1269386</t>
+          <t>1402222</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1257374</t>
+          <t>1390248</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1278269</t>
+          <t>1412388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>186554</t>
+          <t>204233</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>138207</t>
+          <t>179617</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>213386</t>
+          <t>231131</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>179530</t>
+          <t>198846</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>146409</t>
+          <t>178354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>205395</t>
+          <t>221232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>366084</t>
+          <t>403079</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>313296</t>
+          <t>371172</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>405725</t>
+          <t>437546</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3264338</t>
+          <t>3315462</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3237506</t>
+          <t>3288564</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3312685</t>
+          <t>3340078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3469528</t>
+          <t>3526143</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3443663</t>
+          <t>3503757</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3502649</t>
+          <t>3546635</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6733867</t>
+          <t>6841605</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6694226</t>
+          <t>6807138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6786655</t>
+          <t>6873512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>94,88%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3450892</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3649058</t>
+          <t>3724989</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3649058</t>
+          <t>3724989</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3649058</t>
+          <t>3724989</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7099951</t>
+          <t>7244684</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7099951</t>
+          <t>7244684</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7099951</t>
+          <t>7244684</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
